--- a/data/works/EN1092.xlsx
+++ b/data/works/EN1092.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AT-CAD\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AT-CAD\data\works\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BCE03906-1821-43CD-9913-94C887764E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EAFD31-719A-4213-8315-9E4C7E29F0DF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="144" windowWidth="21516" windowHeight="16020" activeTab="2" xr2:uid="{F336D65A-C647-494C-A99A-566C7224E381}"/>
+    <workbookView xWindow="0" yWindow="144" windowWidth="21516" windowHeight="16020" activeTab="9" xr2:uid="{F336D65A-C647-494C-A99A-566C7224E381}"/>
   </bookViews>
   <sheets>
     <sheet name="Type" sheetId="17" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="155">
   <si>
     <t>DN</t>
   </si>
@@ -1074,48 +1074,48 @@
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% — акцент1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% — акцент2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% — акцент3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% — акцент4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% — акцент5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% — акцент6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% — акцент1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% — акцент2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% — акцент3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% — акцент4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% — акцент5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% — акцент6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% — акцент1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% — акцент2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% — акцент3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% — акцент4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% — акцент5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% — акцент6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Акцент1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Акцент2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Акцент3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Акцент4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Акцент5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Акцент6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Ввод " xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Вывод" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Вычисление" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Заголовок 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Заголовок 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Заголовок 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Заголовок 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Итог" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Контрольная ячейка" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Название" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Нейтральный" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Плохой" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Пояснение" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Примечание" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Связанная ячейка" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Текст предупреждения" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Хороший" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Akzent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Akzent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Akzent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Akzent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Akzent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Akzent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Ausgabe" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Berechnung" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Eingabe" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Ergebnis" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Erklärender Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Gut" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Notiz" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Schlecht" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Überschrift" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Überschrift 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Überschrift 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Überschrift 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Überschrift 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Verknüpfte Zelle" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Warnender Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Zelle überprüfen" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1131,9 +1131,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1171,7 +1171,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1277,7 +1277,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1462,7 +1462,7 @@
       <we:containsCustomFunctions/>
     </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
-      <we:customFunctionIdList>
+      <we:customFunctionIdList xmlns="">
         <we:customFunctionIds>_xldudf_AI_TABLE</we:customFunctionIds>
         <we:customFunctionIds>_xldudf_AI_FILL</we:customFunctionIds>
         <we:customFunctionIds>_xldudf_AI_LIST</we:customFunctionIds>
@@ -1480,7 +1480,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEC9A304-6A52-49C5-B574-ACF3B8E9DBF6}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="9"/>
     <col min="2" max="2" width="33.77734375" style="9" customWidth="1"/>
@@ -1705,13 +1705,13 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35037206-009F-4D6A-B80B-5690478BCA02}">
-  <dimension ref="A1:AD26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:AE26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1755,55 +1755,58 @@
         <v>10</v>
       </c>
       <c r="O1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="U1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="V1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="W1" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:31">
       <c r="A2" s="1">
         <v>10</v>
       </c>
@@ -1844,58 +1847,61 @@
         <v>16</v>
       </c>
       <c r="N2" s="1">
+        <v>16</v>
+      </c>
+      <c r="O2" s="1">
         <v>3</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="1">
+      <c r="P2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="1">
         <v>22</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="R2" s="1">
         <v>35</v>
       </c>
-      <c r="R2" s="1">
+      <c r="S2" s="1">
+        <v>6</v>
+      </c>
+      <c r="T2" s="1">
+        <v>35</v>
+      </c>
+      <c r="U2" s="1">
         <v>28</v>
       </c>
-      <c r="S2" s="1">
+      <c r="V2" s="1">
         <v>30</v>
       </c>
-      <c r="T2" s="1">
+      <c r="W2" s="1">
         <v>28</v>
       </c>
-      <c r="U2" s="1">
+      <c r="X2" s="1">
         <v>4</v>
       </c>
-      <c r="V2" s="1">
+      <c r="Y2" s="1">
         <v>40</v>
       </c>
-      <c r="W2" s="1">
-        <v>6</v>
-      </c>
-      <c r="X2" s="1">
-        <v>35</v>
-      </c>
-      <c r="Y2" s="1">
+      <c r="Z2" s="1">
         <v>12</v>
       </c>
-      <c r="Z2" s="1">
+      <c r="AA2" s="1">
         <v>5</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="AB2" s="1">
         <v>1.8</v>
       </c>
-      <c r="AB2" s="7">
+      <c r="AC2" s="7">
         <v>17.2</v>
-      </c>
-      <c r="AC2" s="7">
-        <v>2</v>
       </c>
       <c r="AD2" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:30">
+      <c r="AE2" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
       <c r="A3" s="1">
         <v>15</v>
       </c>
@@ -1936,58 +1942,61 @@
         <v>16</v>
       </c>
       <c r="N3" s="1">
+        <v>16</v>
+      </c>
+      <c r="O3" s="1">
         <v>3</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P3" s="1">
+      <c r="P3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="1">
         <v>22</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="R3" s="1">
         <v>38</v>
       </c>
-      <c r="R3" s="1">
+      <c r="S3" s="1">
+        <v>6</v>
+      </c>
+      <c r="T3" s="1">
+        <v>38</v>
+      </c>
+      <c r="U3" s="1">
         <v>32</v>
       </c>
-      <c r="S3" s="1">
+      <c r="V3" s="1">
         <v>35</v>
       </c>
-      <c r="T3" s="1">
+      <c r="W3" s="1">
         <v>32</v>
       </c>
-      <c r="U3" s="1">
+      <c r="X3" s="1">
         <v>4</v>
       </c>
-      <c r="V3" s="1">
+      <c r="Y3" s="1">
         <v>45</v>
       </c>
-      <c r="W3" s="1">
-        <v>6</v>
-      </c>
-      <c r="X3" s="1">
-        <v>38</v>
-      </c>
-      <c r="Y3" s="1">
+      <c r="Z3" s="1">
         <v>12</v>
       </c>
-      <c r="Z3" s="1">
+      <c r="AA3" s="1">
         <v>5</v>
       </c>
-      <c r="AA3" s="1">
+      <c r="AB3" s="1">
         <v>2</v>
       </c>
-      <c r="AB3" s="7">
+      <c r="AC3" s="7">
         <v>21.3</v>
-      </c>
-      <c r="AC3" s="7">
-        <v>2</v>
       </c>
       <c r="AD3" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:30">
+      <c r="AE3" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31">
       <c r="A4" s="1">
         <v>20</v>
       </c>
@@ -2028,58 +2037,61 @@
         <v>18</v>
       </c>
       <c r="N4" s="1">
+        <v>18</v>
+      </c>
+      <c r="O4" s="1">
         <v>4</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P4" s="1">
+      <c r="P4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q4" s="1">
         <v>26</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>40</v>
       </c>
       <c r="R4" s="1">
         <v>40</v>
       </c>
       <c r="S4" s="1">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="T4" s="1">
         <v>40</v>
       </c>
       <c r="U4" s="1">
+        <v>40</v>
+      </c>
+      <c r="V4" s="1">
+        <v>45</v>
+      </c>
+      <c r="W4" s="1">
+        <v>40</v>
+      </c>
+      <c r="X4" s="1">
         <v>4</v>
       </c>
-      <c r="V4" s="1">
+      <c r="Y4" s="1">
         <v>58</v>
       </c>
-      <c r="W4" s="1">
+      <c r="Z4" s="1">
+        <v>14</v>
+      </c>
+      <c r="AA4" s="1">
         <v>6</v>
       </c>
-      <c r="X4" s="1">
-        <v>40</v>
-      </c>
-      <c r="Y4" s="1">
-        <v>14</v>
-      </c>
-      <c r="Z4" s="1">
-        <v>6</v>
-      </c>
-      <c r="AA4" s="1">
+      <c r="AB4" s="1">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AB4" s="7">
+      <c r="AC4" s="7">
         <v>26.9</v>
-      </c>
-      <c r="AC4" s="7">
-        <v>2.2999999999999998</v>
       </c>
       <c r="AD4" s="7">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="5" spans="1:30">
+      <c r="AE4" s="7">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
       <c r="A5" s="1">
         <v>25</v>
       </c>
@@ -2120,58 +2132,61 @@
         <v>18</v>
       </c>
       <c r="N5" s="1">
+        <v>18</v>
+      </c>
+      <c r="O5" s="1">
         <v>4</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" s="1">
+      <c r="P5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="1">
         <v>28</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="R5" s="1">
         <v>40</v>
       </c>
-      <c r="R5" s="1">
+      <c r="S5" s="1">
+        <v>6</v>
+      </c>
+      <c r="T5" s="1">
+        <v>40</v>
+      </c>
+      <c r="U5" s="1">
         <v>46</v>
       </c>
-      <c r="S5" s="1">
+      <c r="V5" s="1">
         <v>52</v>
       </c>
-      <c r="T5" s="1">
+      <c r="W5" s="1">
         <v>50</v>
       </c>
-      <c r="U5" s="1">
+      <c r="X5" s="1">
         <v>4</v>
       </c>
-      <c r="V5" s="1">
+      <c r="Y5" s="1">
         <v>68</v>
       </c>
-      <c r="W5" s="1">
-        <v>6</v>
-      </c>
-      <c r="X5" s="1">
-        <v>40</v>
-      </c>
-      <c r="Y5" s="1">
+      <c r="Z5" s="1">
         <v>14</v>
       </c>
-      <c r="Z5" s="1">
+      <c r="AA5" s="1">
         <v>7</v>
       </c>
-      <c r="AA5" s="1">
+      <c r="AB5" s="1">
         <v>2.6</v>
       </c>
-      <c r="AB5" s="7">
+      <c r="AC5" s="7">
         <v>33.700000000000003</v>
-      </c>
-      <c r="AC5" s="7">
-        <v>2.6</v>
       </c>
       <c r="AD5" s="7">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="6" spans="1:30">
+      <c r="AE5" s="7">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31">
       <c r="A6" s="1">
         <v>32</v>
       </c>
@@ -2212,58 +2227,61 @@
         <v>18</v>
       </c>
       <c r="N6" s="1">
+        <v>18</v>
+      </c>
+      <c r="O6" s="1">
         <v>5</v>
       </c>
-      <c r="O6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P6" s="1">
+      <c r="P6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="1">
         <v>30</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="R6" s="1">
         <v>42</v>
       </c>
-      <c r="R6" s="1">
+      <c r="S6" s="1">
+        <v>6</v>
+      </c>
+      <c r="T6" s="1">
+        <v>42</v>
+      </c>
+      <c r="U6" s="1">
         <v>56</v>
       </c>
-      <c r="S6" s="1">
+      <c r="V6" s="1">
         <v>60</v>
       </c>
-      <c r="T6" s="1">
+      <c r="W6" s="1">
         <v>60</v>
       </c>
-      <c r="U6" s="1">
+      <c r="X6" s="1">
         <v>6</v>
       </c>
-      <c r="V6" s="1">
+      <c r="Y6" s="1">
         <v>78</v>
       </c>
-      <c r="W6" s="1">
-        <v>6</v>
-      </c>
-      <c r="X6" s="1">
-        <v>42</v>
-      </c>
-      <c r="Y6" s="1">
+      <c r="Z6" s="1">
         <v>14</v>
       </c>
-      <c r="Z6" s="1">
+      <c r="AA6" s="1">
         <v>8</v>
       </c>
-      <c r="AA6" s="1">
+      <c r="AB6" s="1">
         <v>2.6</v>
       </c>
-      <c r="AB6" s="7">
+      <c r="AC6" s="7">
         <v>42.4</v>
-      </c>
-      <c r="AC6" s="7">
-        <v>2.6</v>
       </c>
       <c r="AD6" s="7">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="7" spans="1:30">
+      <c r="AE6" s="7">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31">
       <c r="A7" s="1">
         <v>40</v>
       </c>
@@ -2304,58 +2322,61 @@
         <v>18</v>
       </c>
       <c r="N7" s="1">
+        <v>18</v>
+      </c>
+      <c r="O7" s="1">
         <v>5</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P7" s="1">
+      <c r="P7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q7" s="1">
         <v>32</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="R7" s="1">
         <v>45</v>
       </c>
-      <c r="R7" s="1">
+      <c r="S7" s="1">
+        <v>7</v>
+      </c>
+      <c r="T7" s="1">
+        <v>45</v>
+      </c>
+      <c r="U7" s="1">
         <v>64</v>
       </c>
-      <c r="S7" s="1">
+      <c r="V7" s="1">
         <v>70</v>
       </c>
-      <c r="T7" s="1">
+      <c r="W7" s="1">
         <v>70</v>
       </c>
-      <c r="U7" s="1">
+      <c r="X7" s="1">
         <v>6</v>
       </c>
-      <c r="V7" s="1">
+      <c r="Y7" s="1">
         <v>88</v>
       </c>
-      <c r="W7" s="1">
-        <v>7</v>
-      </c>
-      <c r="X7" s="1">
-        <v>45</v>
-      </c>
-      <c r="Y7" s="1">
+      <c r="Z7" s="1">
         <v>14</v>
       </c>
-      <c r="Z7" s="1">
+      <c r="AA7" s="1">
         <v>8</v>
       </c>
-      <c r="AA7" s="1">
+      <c r="AB7" s="1">
         <v>2.6</v>
       </c>
-      <c r="AB7" s="7">
+      <c r="AC7" s="7">
         <v>48.3</v>
-      </c>
-      <c r="AC7" s="7">
-        <v>2.6</v>
       </c>
       <c r="AD7" s="7">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="8" spans="1:30">
+      <c r="AE7" s="7">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31">
       <c r="A8" s="1">
         <v>50</v>
       </c>
@@ -2396,58 +2417,61 @@
         <v>20</v>
       </c>
       <c r="N8" s="1">
+        <v>20</v>
+      </c>
+      <c r="O8" s="1">
         <v>5</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="P8" s="1">
+      <c r="P8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="1">
         <v>34</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="R8" s="1">
         <v>48</v>
       </c>
-      <c r="R8" s="1">
+      <c r="S8" s="1">
+        <v>8</v>
+      </c>
+      <c r="T8" s="1">
+        <v>48</v>
+      </c>
+      <c r="U8" s="1">
         <v>75</v>
       </c>
-      <c r="S8" s="1">
+      <c r="V8" s="1">
         <v>84</v>
       </c>
-      <c r="T8" s="1">
+      <c r="W8" s="1">
         <v>84</v>
       </c>
-      <c r="U8" s="1">
+      <c r="X8" s="1">
         <v>6</v>
       </c>
-      <c r="V8" s="1">
+      <c r="Y8" s="1">
         <v>102</v>
       </c>
-      <c r="W8" s="1">
-        <v>8</v>
-      </c>
-      <c r="X8" s="1">
-        <v>48</v>
-      </c>
-      <c r="Y8" s="1">
+      <c r="Z8" s="1">
         <v>16</v>
       </c>
-      <c r="Z8" s="1">
+      <c r="AA8" s="1">
         <v>10</v>
       </c>
-      <c r="AA8" s="1">
+      <c r="AB8" s="1">
         <v>2.9</v>
       </c>
-      <c r="AB8" s="7">
+      <c r="AC8" s="7">
         <v>60.3</v>
-      </c>
-      <c r="AC8" s="7">
-        <v>2.9</v>
       </c>
       <c r="AD8" s="7">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:30">
+      <c r="AE8" s="7">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31">
       <c r="A9" s="1">
         <v>65</v>
       </c>
@@ -2488,58 +2512,61 @@
         <v>22</v>
       </c>
       <c r="N9" s="1">
+        <v>22</v>
+      </c>
+      <c r="O9" s="1">
         <v>6</v>
       </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
         <v>55</v>
       </c>
-      <c r="P9" s="1">
+      <c r="Q9" s="1">
         <v>38</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="R9" s="1">
         <v>52</v>
       </c>
-      <c r="R9" s="1">
+      <c r="S9" s="1">
+        <v>10</v>
+      </c>
+      <c r="T9" s="1">
+        <v>52</v>
+      </c>
+      <c r="U9" s="1">
         <v>90</v>
       </c>
-      <c r="S9" s="1">
+      <c r="V9" s="1">
         <v>104</v>
       </c>
-      <c r="T9" s="1">
+      <c r="W9" s="1">
         <v>104</v>
       </c>
-      <c r="U9" s="1">
+      <c r="X9" s="1">
         <v>6</v>
       </c>
-      <c r="V9" s="1">
+      <c r="Y9" s="1">
         <v>122</v>
       </c>
-      <c r="W9" s="1">
-        <v>10</v>
-      </c>
-      <c r="X9" s="1">
-        <v>52</v>
-      </c>
-      <c r="Y9" s="1">
+      <c r="Z9" s="1">
         <v>16</v>
       </c>
-      <c r="Z9" s="1">
+      <c r="AA9" s="1">
         <v>11</v>
       </c>
-      <c r="AA9" s="1">
+      <c r="AB9" s="1">
         <v>2.9</v>
       </c>
-      <c r="AB9" s="7">
+      <c r="AC9" s="7">
         <v>76.099999999999994</v>
-      </c>
-      <c r="AC9" s="7">
-        <v>2.9</v>
       </c>
       <c r="AD9" s="7">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="10" spans="1:30">
+      <c r="AE9" s="7">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31">
       <c r="A10" s="1">
         <v>80</v>
       </c>
@@ -2580,58 +2607,61 @@
         <v>24</v>
       </c>
       <c r="N10" s="1">
+        <v>24</v>
+      </c>
+      <c r="O10" s="1">
         <v>6</v>
       </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
         <v>70</v>
       </c>
-      <c r="P10" s="1">
+      <c r="Q10" s="1">
         <v>40</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="R10" s="1">
         <v>58</v>
       </c>
-      <c r="R10" s="1">
+      <c r="S10" s="1">
+        <v>12</v>
+      </c>
+      <c r="T10" s="1">
+        <v>58</v>
+      </c>
+      <c r="U10" s="1">
         <v>105</v>
       </c>
-      <c r="S10" s="1">
+      <c r="V10" s="1">
         <v>118</v>
       </c>
-      <c r="T10" s="1">
+      <c r="W10" s="1">
         <v>120</v>
       </c>
-      <c r="U10" s="1">
+      <c r="X10" s="1">
         <v>8</v>
       </c>
-      <c r="V10" s="1">
+      <c r="Y10" s="1">
         <v>138</v>
       </c>
-      <c r="W10" s="1">
+      <c r="Z10" s="1">
+        <v>18</v>
+      </c>
+      <c r="AA10" s="1">
         <v>12</v>
       </c>
-      <c r="X10" s="1">
-        <v>58</v>
-      </c>
-      <c r="Y10" s="1">
-        <v>18</v>
-      </c>
-      <c r="Z10" s="1">
-        <v>12</v>
-      </c>
-      <c r="AA10" s="1">
+      <c r="AB10" s="1">
         <v>3.2</v>
       </c>
-      <c r="AB10" s="7">
+      <c r="AC10" s="7">
         <v>88.9</v>
-      </c>
-      <c r="AC10" s="7">
-        <v>3.2</v>
       </c>
       <c r="AD10" s="7">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="11" spans="1:30">
+      <c r="AE10" s="7">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
       <c r="A11" s="1">
         <v>100</v>
       </c>
@@ -2672,58 +2702,61 @@
         <v>24</v>
       </c>
       <c r="N11" s="1">
+        <v>24</v>
+      </c>
+      <c r="O11" s="1">
         <v>6</v>
       </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
         <v>90</v>
       </c>
-      <c r="P11" s="1">
+      <c r="Q11" s="1">
         <v>44</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="R11" s="1">
         <v>65</v>
       </c>
-      <c r="R11" s="1">
+      <c r="S11" s="1">
+        <v>12</v>
+      </c>
+      <c r="T11" s="1">
+        <v>65</v>
+      </c>
+      <c r="U11" s="1">
         <v>134</v>
       </c>
-      <c r="S11" s="1">
+      <c r="V11" s="1">
         <v>145</v>
       </c>
-      <c r="T11" s="1">
+      <c r="W11" s="1">
         <v>142</v>
       </c>
-      <c r="U11" s="1">
+      <c r="X11" s="1">
         <v>8</v>
       </c>
-      <c r="V11" s="1">
+      <c r="Y11" s="1">
         <v>162</v>
       </c>
-      <c r="W11" s="1">
-        <v>12</v>
-      </c>
-      <c r="X11" s="1">
-        <v>65</v>
-      </c>
-      <c r="Y11" s="1">
+      <c r="Z11" s="1">
         <v>20</v>
       </c>
-      <c r="Z11" s="1">
+      <c r="AA11" s="1">
         <v>14</v>
       </c>
-      <c r="AA11" s="1">
+      <c r="AB11" s="1">
         <v>3.6</v>
       </c>
-      <c r="AB11" s="7">
+      <c r="AC11" s="7">
         <v>114.3</v>
-      </c>
-      <c r="AC11" s="7">
-        <v>3.6</v>
       </c>
       <c r="AD11" s="7">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="12" spans="1:30">
+      <c r="AE11" s="7">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31">
       <c r="A12" s="1">
         <v>125</v>
       </c>
@@ -2764,58 +2797,61 @@
         <v>26</v>
       </c>
       <c r="N12" s="1">
+        <v>26</v>
+      </c>
+      <c r="O12" s="1">
         <v>6</v>
       </c>
-      <c r="O12" s="1">
+      <c r="P12" s="1">
         <v>115</v>
       </c>
-      <c r="P12" s="1">
+      <c r="Q12" s="1">
         <v>48</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="R12" s="1">
         <v>68</v>
       </c>
-      <c r="R12" s="1">
+      <c r="S12" s="1">
+        <v>12</v>
+      </c>
+      <c r="T12" s="1">
+        <v>68</v>
+      </c>
+      <c r="U12" s="1">
         <v>162</v>
       </c>
-      <c r="S12" s="1">
+      <c r="V12" s="1">
         <v>170</v>
       </c>
-      <c r="T12" s="1">
+      <c r="W12" s="1">
         <v>162</v>
       </c>
-      <c r="U12" s="1">
+      <c r="X12" s="1">
         <v>8</v>
       </c>
-      <c r="V12" s="1">
+      <c r="Y12" s="1">
         <v>188</v>
       </c>
-      <c r="W12" s="1">
-        <v>12</v>
-      </c>
-      <c r="X12" s="1">
-        <v>68</v>
-      </c>
-      <c r="Y12" s="1">
+      <c r="Z12" s="1">
         <v>22</v>
       </c>
-      <c r="Z12" s="1">
+      <c r="AA12" s="1">
         <v>16</v>
       </c>
-      <c r="AA12" s="1">
+      <c r="AB12" s="1">
         <v>4</v>
       </c>
-      <c r="AB12" s="7">
+      <c r="AC12" s="7">
         <v>139.69999999999999</v>
-      </c>
-      <c r="AC12" s="7">
-        <v>4</v>
       </c>
       <c r="AD12" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:30">
+      <c r="AE12" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31">
       <c r="A13" s="1">
         <v>150</v>
       </c>
@@ -2856,58 +2892,61 @@
         <v>28</v>
       </c>
       <c r="N13" s="1">
+        <v>28</v>
+      </c>
+      <c r="O13" s="1">
         <v>6</v>
       </c>
-      <c r="O13" s="1">
+      <c r="P13" s="1">
         <v>140</v>
       </c>
-      <c r="P13" s="1">
+      <c r="Q13" s="1">
         <v>52</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="R13" s="1">
         <v>75</v>
       </c>
-      <c r="R13" s="1">
+      <c r="S13" s="1">
+        <v>12</v>
+      </c>
+      <c r="T13" s="1">
+        <v>75</v>
+      </c>
+      <c r="U13" s="1">
         <v>192</v>
       </c>
-      <c r="S13" s="1">
+      <c r="V13" s="1">
         <v>200</v>
       </c>
-      <c r="T13" s="1">
+      <c r="W13" s="1">
         <v>192</v>
       </c>
-      <c r="U13" s="1">
+      <c r="X13" s="1">
         <v>10</v>
       </c>
-      <c r="V13" s="1">
+      <c r="Y13" s="1">
         <v>218</v>
       </c>
-      <c r="W13" s="1">
-        <v>12</v>
-      </c>
-      <c r="X13" s="1">
-        <v>75</v>
-      </c>
-      <c r="Y13" s="1">
+      <c r="Z13" s="1">
         <v>24</v>
       </c>
-      <c r="Z13" s="1">
-        <v>18</v>
-      </c>
       <c r="AA13" s="1">
+        <v>18</v>
+      </c>
+      <c r="AB13" s="1">
         <v>4.5</v>
       </c>
-      <c r="AB13" s="7">
+      <c r="AC13" s="7">
         <v>168.3</v>
-      </c>
-      <c r="AC13" s="7">
-        <v>4.5</v>
       </c>
       <c r="AD13" s="7">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:30">
+      <c r="AE13" s="7">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31">
       <c r="A14" s="1">
         <v>200</v>
       </c>
@@ -2945,61 +2984,64 @@
         <v>34</v>
       </c>
       <c r="M14" s="1">
+        <v>34</v>
+      </c>
+      <c r="N14" s="1">
         <v>36</v>
       </c>
-      <c r="N14" s="1">
+      <c r="O14" s="1">
         <v>6</v>
       </c>
-      <c r="O14" s="1">
+      <c r="P14" s="1">
         <v>190</v>
       </c>
-      <c r="P14" s="1">
+      <c r="Q14" s="1">
         <v>52</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="R14" s="1">
         <v>88</v>
       </c>
-      <c r="R14" s="1">
+      <c r="S14" s="1">
+        <v>16</v>
+      </c>
+      <c r="T14" s="1">
+        <v>88</v>
+      </c>
+      <c r="U14" s="1">
         <v>244</v>
       </c>
-      <c r="S14" s="1">
+      <c r="V14" s="1">
         <v>260</v>
       </c>
-      <c r="T14" s="1">
+      <c r="W14" s="1">
         <v>254</v>
       </c>
-      <c r="U14" s="1">
+      <c r="X14" s="1">
         <v>10</v>
       </c>
-      <c r="V14" s="1">
+      <c r="Y14" s="1">
         <v>285</v>
       </c>
-      <c r="W14" s="1">
-        <v>16</v>
-      </c>
-      <c r="X14" s="1">
-        <v>88</v>
-      </c>
-      <c r="Y14" s="1">
+      <c r="Z14" s="1">
         <v>28</v>
       </c>
-      <c r="Z14" s="1">
+      <c r="AA14" s="1">
         <v>20</v>
       </c>
-      <c r="AA14" s="1">
+      <c r="AB14" s="1">
         <v>6.3</v>
       </c>
-      <c r="AB14" s="7">
+      <c r="AC14" s="7">
         <v>219.1</v>
-      </c>
-      <c r="AC14" s="7">
-        <v>6.3</v>
       </c>
       <c r="AD14" s="7">
         <v>6.3</v>
       </c>
-    </row>
-    <row r="15" spans="1:30">
+      <c r="AE14" s="7">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31">
       <c r="A15" s="1">
         <v>250</v>
       </c>
@@ -3040,58 +3082,61 @@
         <v>38</v>
       </c>
       <c r="N15" s="1">
+        <v>38</v>
+      </c>
+      <c r="O15" s="1">
         <v>8</v>
       </c>
-      <c r="O15" s="1">
+      <c r="P15" s="1">
         <v>235</v>
       </c>
-      <c r="P15" s="1">
+      <c r="Q15" s="1">
         <v>60</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="R15" s="1">
         <v>105</v>
       </c>
-      <c r="R15" s="1">
+      <c r="S15" s="1">
+        <v>18</v>
+      </c>
+      <c r="T15" s="1">
+        <v>105</v>
+      </c>
+      <c r="U15" s="1">
         <v>306</v>
       </c>
-      <c r="S15" s="1">
+      <c r="V15" s="1">
         <v>312</v>
       </c>
-      <c r="T15" s="1">
+      <c r="W15" s="1">
         <v>312</v>
       </c>
-      <c r="U15" s="1">
+      <c r="X15" s="1">
         <v>12</v>
       </c>
-      <c r="V15" s="1">
+      <c r="Y15" s="1">
         <v>345</v>
       </c>
-      <c r="W15" s="1">
-        <v>18</v>
-      </c>
-      <c r="X15" s="1">
-        <v>105</v>
-      </c>
-      <c r="Y15" s="1">
+      <c r="Z15" s="1">
         <v>30</v>
       </c>
-      <c r="Z15" s="1">
+      <c r="AA15" s="1">
         <v>22</v>
       </c>
-      <c r="AA15" s="1">
+      <c r="AB15" s="1">
         <v>7.1</v>
       </c>
-      <c r="AB15" s="7">
+      <c r="AC15" s="7">
         <v>273</v>
-      </c>
-      <c r="AC15" s="7">
-        <v>7.1</v>
       </c>
       <c r="AD15" s="7">
         <v>7.1</v>
       </c>
-    </row>
-    <row r="16" spans="1:30">
+      <c r="AE15" s="7">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31">
       <c r="A16" s="1">
         <v>300</v>
       </c>
@@ -3132,58 +3177,61 @@
         <v>42</v>
       </c>
       <c r="N16" s="1">
+        <v>42</v>
+      </c>
+      <c r="O16" s="1">
         <v>8</v>
       </c>
-      <c r="O16" s="1">
+      <c r="P16" s="1">
         <v>285</v>
       </c>
-      <c r="P16" s="1">
+      <c r="Q16" s="1">
         <v>67</v>
       </c>
-      <c r="Q16" s="1">
+      <c r="R16" s="1">
         <v>115</v>
       </c>
-      <c r="R16" s="1">
+      <c r="S16" s="1">
+        <v>18</v>
+      </c>
+      <c r="T16" s="1">
+        <v>115</v>
+      </c>
+      <c r="U16" s="1">
         <v>362</v>
       </c>
-      <c r="S16" s="1">
+      <c r="V16" s="1">
         <v>380</v>
       </c>
-      <c r="T16" s="1">
+      <c r="W16" s="1">
         <v>378</v>
       </c>
-      <c r="U16" s="1">
+      <c r="X16" s="1">
         <v>12</v>
       </c>
-      <c r="V16" s="1">
+      <c r="Y16" s="1">
         <v>410</v>
       </c>
-      <c r="W16" s="1">
-        <v>18</v>
-      </c>
-      <c r="X16" s="1">
-        <v>115</v>
-      </c>
-      <c r="Y16" s="1">
+      <c r="Z16" s="1">
         <v>34</v>
       </c>
-      <c r="Z16" s="1">
+      <c r="AA16" s="1">
         <v>25</v>
       </c>
-      <c r="AA16" s="1">
+      <c r="AB16" s="1">
         <v>8</v>
       </c>
-      <c r="AB16" s="7">
+      <c r="AC16" s="7">
         <v>323.89999999999998</v>
-      </c>
-      <c r="AC16" s="7">
-        <v>8</v>
       </c>
       <c r="AD16" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:30">
+      <c r="AE16" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31">
       <c r="A17" s="1">
         <v>350</v>
       </c>
@@ -3224,58 +3272,61 @@
         <v>46</v>
       </c>
       <c r="N17" s="1">
+        <v>46</v>
+      </c>
+      <c r="O17" s="1">
         <v>8</v>
       </c>
-      <c r="O17" s="1">
+      <c r="P17" s="1">
         <v>330</v>
       </c>
-      <c r="P17" s="1">
+      <c r="Q17" s="1">
         <v>72</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="R17" s="1">
         <v>125</v>
       </c>
-      <c r="R17" s="1">
+      <c r="S17" s="1">
+        <v>20</v>
+      </c>
+      <c r="T17" s="1">
+        <v>125</v>
+      </c>
+      <c r="U17" s="1">
         <v>408</v>
       </c>
-      <c r="S17" s="1">
+      <c r="V17" s="1">
         <v>424</v>
       </c>
-      <c r="T17" s="1">
+      <c r="W17" s="1">
         <v>432</v>
       </c>
-      <c r="U17" s="1">
+      <c r="X17" s="1">
         <v>12</v>
       </c>
-      <c r="V17" s="1">
+      <c r="Y17" s="1">
         <v>465</v>
       </c>
-      <c r="W17" s="1">
-        <v>20</v>
-      </c>
-      <c r="X17" s="1">
-        <v>125</v>
-      </c>
-      <c r="Y17" s="1">
+      <c r="Z17" s="1">
         <v>36</v>
       </c>
-      <c r="Z17" s="1">
+      <c r="AA17" s="1">
         <v>28</v>
       </c>
-      <c r="AA17" s="1">
+      <c r="AB17" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="AB17" s="7">
+      <c r="AC17" s="7">
         <v>355.6</v>
-      </c>
-      <c r="AC17" s="7">
-        <v>8.8000000000000007</v>
       </c>
       <c r="AD17" s="7">
         <v>8.8000000000000007</v>
       </c>
-    </row>
-    <row r="18" spans="1:30">
+      <c r="AE17" s="7">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31">
       <c r="A18" s="1">
         <v>400</v>
       </c>
@@ -3316,58 +3367,61 @@
         <v>50</v>
       </c>
       <c r="N18" s="1">
+        <v>50</v>
+      </c>
+      <c r="O18" s="1">
         <v>8</v>
       </c>
-      <c r="O18" s="1">
+      <c r="P18" s="1">
         <v>380</v>
       </c>
-      <c r="P18" s="1">
+      <c r="Q18" s="1">
         <v>78</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="R18" s="1">
         <v>135</v>
       </c>
-      <c r="R18" s="1">
+      <c r="S18" s="1">
+        <v>20</v>
+      </c>
+      <c r="T18" s="1">
+        <v>135</v>
+      </c>
+      <c r="U18" s="1">
         <v>462</v>
       </c>
-      <c r="S18" s="1">
+      <c r="V18" s="1">
         <v>478</v>
       </c>
-      <c r="T18" s="1">
+      <c r="W18" s="1">
         <v>498</v>
       </c>
-      <c r="U18" s="1">
+      <c r="X18" s="1">
         <v>12</v>
       </c>
-      <c r="V18" s="1">
+      <c r="Y18" s="1">
         <v>535</v>
       </c>
-      <c r="W18" s="1">
-        <v>20</v>
-      </c>
-      <c r="X18" s="1">
-        <v>135</v>
-      </c>
-      <c r="Y18" s="1">
+      <c r="Z18" s="1">
         <v>42</v>
       </c>
-      <c r="Z18" s="1">
+      <c r="AA18" s="1">
         <v>32</v>
       </c>
-      <c r="AA18" s="1">
+      <c r="AB18" s="1">
         <v>11</v>
       </c>
-      <c r="AB18" s="7">
+      <c r="AC18" s="7">
         <v>406.4</v>
-      </c>
-      <c r="AC18" s="7">
-        <v>11</v>
       </c>
       <c r="AD18" s="7">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:30">
+      <c r="AE18" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31">
       <c r="A19" s="1">
         <v>450</v>
       </c>
@@ -3408,58 +3462,61 @@
         <v>57</v>
       </c>
       <c r="N19" s="1">
+        <v>57</v>
+      </c>
+      <c r="O19" s="1">
         <v>8</v>
       </c>
-      <c r="O19" s="1">
+      <c r="P19" s="1">
         <v>425</v>
       </c>
-      <c r="P19" s="1">
+      <c r="Q19" s="1">
         <v>84</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="R19" s="1">
         <v>135</v>
       </c>
-      <c r="R19" s="1">
+      <c r="S19" s="1">
+        <v>20</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U19" s="1">
         <v>500</v>
       </c>
-      <c r="S19" s="1">
+      <c r="V19" s="1">
         <v>522</v>
       </c>
-      <c r="T19" s="1">
+      <c r="W19" s="1">
         <v>522</v>
       </c>
-      <c r="U19" s="1">
+      <c r="X19" s="1">
         <v>12</v>
       </c>
-      <c r="V19" s="1">
+      <c r="Y19" s="1">
         <v>560</v>
       </c>
-      <c r="W19" s="1">
-        <v>20</v>
-      </c>
-      <c r="X19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y19" s="1">
+      <c r="Z19" s="1">
         <v>46</v>
       </c>
-      <c r="Z19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA19" s="1">
+      <c r="AA19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB19" s="1">
         <v>12.5</v>
       </c>
-      <c r="AB19" s="7">
+      <c r="AC19" s="7">
         <v>457</v>
-      </c>
-      <c r="AC19" s="7">
-        <v>12.5</v>
       </c>
       <c r="AD19" s="7">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="20" spans="1:30">
+      <c r="AE19" s="7">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31">
       <c r="A20" s="1">
         <v>500</v>
       </c>
@@ -3500,58 +3557,61 @@
         <v>57</v>
       </c>
       <c r="N20" s="1">
+        <v>57</v>
+      </c>
+      <c r="O20" s="1">
         <v>8</v>
       </c>
-      <c r="O20" s="1">
+      <c r="P20" s="1">
         <v>475</v>
       </c>
-      <c r="P20" s="1">
+      <c r="Q20" s="1">
         <v>90</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="R20" s="1">
         <v>140</v>
       </c>
-      <c r="R20" s="1">
+      <c r="S20" s="1">
+        <v>20</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U20" s="1">
         <v>562</v>
       </c>
-      <c r="S20" s="1">
+      <c r="V20" s="1">
         <v>576</v>
       </c>
-      <c r="T20" s="1">
+      <c r="W20" s="1">
         <v>576</v>
       </c>
-      <c r="U20" s="1">
+      <c r="X20" s="1">
         <v>12</v>
       </c>
-      <c r="V20" s="1">
+      <c r="Y20" s="1">
         <v>615</v>
       </c>
-      <c r="W20" s="1">
-        <v>20</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y20" s="1">
+      <c r="Z20" s="1">
         <v>50</v>
       </c>
-      <c r="Z20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA20" s="1">
+      <c r="AA20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB20" s="1">
         <v>14.2</v>
       </c>
-      <c r="AB20" s="7">
+      <c r="AC20" s="7">
         <v>508</v>
-      </c>
-      <c r="AC20" s="7">
-        <v>14.2</v>
       </c>
       <c r="AD20" s="7">
         <v>14.2</v>
       </c>
-    </row>
-    <row r="21" spans="1:30">
+      <c r="AE20" s="7">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31">
       <c r="A21" s="1">
         <v>600</v>
       </c>
@@ -3592,58 +3652,61 @@
         <v>72</v>
       </c>
       <c r="N21" s="1">
+        <v>72</v>
+      </c>
+      <c r="O21" s="1">
         <v>8</v>
       </c>
-      <c r="O21" s="1">
+      <c r="P21" s="1">
         <v>575</v>
       </c>
-      <c r="P21" s="1">
+      <c r="Q21" s="1">
         <v>100</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="R21" s="1">
         <v>150</v>
       </c>
-      <c r="R21" s="1">
+      <c r="S21" s="1">
+        <v>20</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U21" s="1">
         <v>666</v>
       </c>
-      <c r="S21" s="1">
+      <c r="V21" s="1">
         <v>686</v>
       </c>
-      <c r="T21" s="1">
+      <c r="W21" s="1">
         <v>686</v>
       </c>
-      <c r="U21" s="1">
+      <c r="X21" s="1">
         <v>12</v>
       </c>
-      <c r="V21" s="1">
+      <c r="Y21" s="1">
         <v>735</v>
       </c>
-      <c r="W21" s="1">
-        <v>20</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y21" s="1">
+      <c r="Z21" s="1">
         <v>54</v>
       </c>
-      <c r="Z21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA21" s="1">
+      <c r="AA21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB21" s="1">
         <v>16</v>
       </c>
-      <c r="AB21" s="7">
+      <c r="AC21" s="7">
         <v>610</v>
-      </c>
-      <c r="AC21" s="7">
-        <v>16</v>
       </c>
       <c r="AD21" s="7">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:30">
+      <c r="AE21" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31">
       <c r="A22" s="1">
         <v>700</v>
       </c>
@@ -3684,58 +3747,61 @@
         <v>50</v>
       </c>
       <c r="N22" s="1">
+        <v>50</v>
+      </c>
+      <c r="O22" s="1">
         <v>8</v>
       </c>
-      <c r="O22" s="1">
+      <c r="P22" s="1">
         <v>380</v>
       </c>
-      <c r="P22" s="1">
+      <c r="Q22" s="1">
         <v>78</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="R22" s="1">
         <v>135</v>
       </c>
-      <c r="R22" s="1">
+      <c r="S22" s="1">
+        <v>20</v>
+      </c>
+      <c r="T22" s="1">
+        <v>135</v>
+      </c>
+      <c r="U22" s="1">
         <v>462</v>
       </c>
-      <c r="S22" s="1">
+      <c r="V22" s="1">
         <v>478</v>
       </c>
-      <c r="T22" s="1">
+      <c r="W22" s="1">
         <v>498</v>
       </c>
-      <c r="U22" s="1">
+      <c r="X22" s="1">
         <v>12</v>
       </c>
-      <c r="V22" s="1">
+      <c r="Y22" s="1">
         <v>840</v>
       </c>
-      <c r="W22" s="1">
-        <v>20</v>
-      </c>
-      <c r="X22" s="1">
-        <v>135</v>
-      </c>
-      <c r="Y22" s="1">
+      <c r="Z22" s="1">
         <v>42</v>
       </c>
-      <c r="Z22" s="1">
+      <c r="AA22" s="1">
         <v>32</v>
       </c>
-      <c r="AA22" s="1">
+      <c r="AB22" s="1">
         <v>11</v>
       </c>
-      <c r="AB22" s="7">
+      <c r="AC22" s="7">
         <v>711</v>
       </c>
-      <c r="AC22" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="AD22" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:30">
+      <c r="AE22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31">
       <c r="A23" s="1">
         <v>800</v>
       </c>
@@ -3776,58 +3842,61 @@
         <v>57</v>
       </c>
       <c r="N23" s="1">
+        <v>57</v>
+      </c>
+      <c r="O23" s="1">
         <v>8</v>
       </c>
-      <c r="O23" s="1">
+      <c r="P23" s="1">
         <v>425</v>
       </c>
-      <c r="P23" s="1">
+      <c r="Q23" s="1">
         <v>84</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="R23" s="1">
         <v>135</v>
       </c>
-      <c r="R23" s="1">
+      <c r="S23" s="1">
+        <v>20</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U23" s="1">
         <v>500</v>
       </c>
-      <c r="S23" s="1">
+      <c r="V23" s="1">
         <v>522</v>
       </c>
-      <c r="T23" s="1">
+      <c r="W23" s="1">
         <v>522</v>
       </c>
-      <c r="U23" s="1">
+      <c r="X23" s="1">
         <v>12</v>
       </c>
-      <c r="V23" s="1">
+      <c r="Y23" s="1">
         <v>960</v>
       </c>
-      <c r="W23" s="1">
-        <v>20</v>
-      </c>
-      <c r="X23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y23" s="1">
+      <c r="Z23" s="1">
         <v>46</v>
       </c>
-      <c r="Z23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA23" s="1">
+      <c r="AA23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB23" s="1">
         <v>12.5</v>
       </c>
-      <c r="AB23" s="7">
+      <c r="AC23" s="7">
         <v>813</v>
       </c>
-      <c r="AC23" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="AD23" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:30">
+      <c r="AE23" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31">
       <c r="A24" s="1">
         <v>900</v>
       </c>
@@ -3868,58 +3937,61 @@
         <v>57</v>
       </c>
       <c r="N24" s="1">
+        <v>57</v>
+      </c>
+      <c r="O24" s="1">
         <v>8</v>
       </c>
-      <c r="O24" s="1">
+      <c r="P24" s="1">
         <v>475</v>
       </c>
-      <c r="P24" s="1">
+      <c r="Q24" s="1">
         <v>90</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="R24" s="1">
         <v>140</v>
       </c>
-      <c r="R24" s="1">
+      <c r="S24" s="1">
+        <v>20</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U24" s="1">
         <v>562</v>
       </c>
-      <c r="S24" s="1">
+      <c r="V24" s="1">
         <v>576</v>
       </c>
-      <c r="T24" s="1">
+      <c r="W24" s="1">
         <v>576</v>
       </c>
-      <c r="U24" s="1">
+      <c r="X24" s="1">
         <v>12</v>
       </c>
-      <c r="V24" s="1">
+      <c r="Y24" s="1">
         <v>1070</v>
       </c>
-      <c r="W24" s="1">
-        <v>20</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y24" s="1">
+      <c r="Z24" s="1">
         <v>50</v>
       </c>
-      <c r="Z24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA24" s="1">
+      <c r="AA24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB24" s="1">
         <v>14.2</v>
       </c>
-      <c r="AB24" s="7">
+      <c r="AC24" s="7">
         <v>914</v>
       </c>
-      <c r="AC24" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="AD24" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:30">
+      <c r="AE24" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31">
       <c r="A25" s="1">
         <v>1000</v>
       </c>
@@ -3960,59 +4032,62 @@
         <v>72</v>
       </c>
       <c r="N25" s="1">
+        <v>72</v>
+      </c>
+      <c r="O25" s="1">
         <v>8</v>
       </c>
-      <c r="O25" s="1">
+      <c r="P25" s="1">
         <v>575</v>
       </c>
-      <c r="P25" s="1">
+      <c r="Q25" s="1">
         <v>100</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="R25" s="1">
         <v>150</v>
       </c>
-      <c r="R25" s="1">
+      <c r="S25" s="1">
+        <v>20</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U25" s="1">
         <v>666</v>
       </c>
-      <c r="S25" s="1">
+      <c r="V25" s="1">
         <v>686</v>
       </c>
-      <c r="T25" s="1">
+      <c r="W25" s="1">
         <v>686</v>
       </c>
-      <c r="U25" s="1">
+      <c r="X25" s="1">
         <v>12</v>
       </c>
-      <c r="V25" s="1">
+      <c r="Y25" s="1">
         <v>1180</v>
       </c>
-      <c r="W25" s="1">
-        <v>20</v>
-      </c>
-      <c r="X25" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y25" s="1">
+      <c r="Z25" s="1">
         <v>54</v>
       </c>
-      <c r="Z25" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA25" s="1">
+      <c r="AA25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB25" s="1">
         <v>16</v>
       </c>
-      <c r="AB25" s="8">
+      <c r="AC25" s="8">
         <v>1016</v>
       </c>
-      <c r="AC25" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="AD25" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:30">
-      <c r="AB26" s="3"/>
+      <c r="AE25" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31">
+      <c r="AC26" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4022,7 +4097,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F99C2890-E46B-4CD6-A4B7-1FD5601475D6}">
   <dimension ref="A1:X26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="4" t="s">
@@ -5389,7 +5464,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC3E8B1C-4591-4A47-84C7-EEA3FFEB8978}">
   <dimension ref="A1:X18"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="4" t="s">
@@ -6660,7 +6735,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9DFAE3-5B90-4788-BB66-9B61C00558F0}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="4" t="s">
@@ -7496,7 +7571,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E471143D-EE0A-4D60-94B7-C597E145E3FA}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="1"/>
   </cols>
@@ -8335,7 +8410,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868053FB-1FB1-425F-B8AA-938FB3CAD603}">
   <dimension ref="A1:S13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="4" t="s">
@@ -9112,7 +9187,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A5AAEA-9B0F-4C01-A485-06D962D3B7C7}">
   <dimension ref="A1:S12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="4" t="s">
@@ -9830,7 +9905,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D7F83A1-C1FE-4433-87D1-40AE7E9E2A75}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.77734375" bestFit="1" customWidth="1"/>
@@ -9985,7 +10060,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E2565B7-07F9-4364-850F-F61FE9874237}">
   <dimension ref="A1:AM24"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4.5546875" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="2.21875" style="1" bestFit="1" customWidth="1"/>
@@ -12875,7 +12950,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE2DC567-4662-4919-B9F3-5A560DE23C7B}">
   <dimension ref="A1:K56"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="4" t="s">
@@ -14477,7 +14552,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD3D9BE8-503B-4DBF-A2D8-824144F1C733}">
   <dimension ref="A1:AD40"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="1"/>
   </cols>
@@ -18170,7 +18245,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA78A134-2494-4F0A-A5CD-BA7DC18DA2C1}">
   <dimension ref="A1:AG38"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="1"/>
   </cols>
@@ -22021,7 +22096,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF7B8C90-21AE-48FE-BB4D-3B50581D0BE4}">
   <dimension ref="A1:AI35"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="1"/>
   </cols>
@@ -25776,7 +25851,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D2BD751-FEC8-452A-BB25-C23763EC9DC3}">
   <dimension ref="A1:AI30"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="1"/>
   </cols>
@@ -28999,7 +29074,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E8007F-8DF9-44A6-AA19-3B0F0F51A8F4}">
   <dimension ref="A1:AE33"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="1"/>
   </cols>
